--- a/Thesaurus/CV_TermUpdate_Tracker.xlsx
+++ b/Thesaurus/CV_TermUpdate_Tracker.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Terms" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Terms" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Issues" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF41"/>
+  <dimension ref="A1:AF132"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.88" customWidth="1" style="9" min="1" max="1"/>
@@ -1973,6 +1973,3676 @@
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>Open access</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>The resource is publicly accessible without restriction.</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>Access levels</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M42" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>Restricted access</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>Access to the resource is limited to specific users or requires permission from the rights holder or data custodian.</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>Access levels</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M43" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>Closed access</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>The resource is not accessible to users outside the data-holding organisation.</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>Access levels</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M44" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Scanning</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>The digital representation was created using a flatbed or sheet-fed scanner.</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>Digitisation methods</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M45" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>The digital representation was created by photographing the original with a camera.</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>Digitisation methods</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M46" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>Photogrammetry</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>The digital representation was created by combining multiple photographs to produce a measured or georeferenced output.</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>Digitisation methods</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M47" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>Born digital</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>The resource was created directly in digital form, with no physical original.</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>Digitisation methods</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M48" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>The digitisation method used is not covered by the terms currently in this vocabulary.</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>Digitisation methods</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>The document is in good physical condition, with no significant damage or deterioration.</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>Document conditions</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>The document shows some signs of wear or minor damage but remains fully usable.</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>Document conditions</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>The document is significantly damaged or deteriorated, affecting its usability.</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>Document conditions</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M52" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>Damaged</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>The document has sustained physical damage, such as tears, water damage, or staining.</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>Document conditions</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M53" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>Fragile</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>The document is intact but physically weak and requires careful handling to avoid further damage.</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>Document conditions</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M54" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>The condition of the document has not been assessed or recorded.</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>Document conditions</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M55" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>This licence lets others distribute, remix, adapt, and build upon your work, even commercially, as long as they credit you for the original creation. This is the most accommodating of licences offered. Recommended for maximum dissemination and use of licenced materials.</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M56" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>This license enables reusers to distribute, remix, adapt, and build upon the material in any medium or format for noncommercial purposes only, and only so long as attribution is given to the creator.</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by-nc/4.0/deed.en</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M57" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>This licence is the most restrictive of our six main licences, only allowing others to download your works and share them with others as long as they credit you, but they can’t change them in any way or use them commercially.</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by-nc-nd/4.0/deed.en</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M58" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>This licence lets others remix, adapt, and build upon your work non-commercially, as long as they credit you and licence their new creations under the identical terms.</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by-nc-sa/4.0/deed.en</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M59" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>CC BY-ND</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>This licence lets others reuse the work for any purpose, including commercially; however, it cannot be shared with others in adapted form, and credit must be provided to you.</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by-nd/4.0/deed.en</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M60" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>CC BY-SA</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>This licence lets others remix, adapt, and build upon your work even for commercial purposes, as long as they credit you and licence their new creations under the identical terms. This licence is often compared to “copyleft” free and open source software licences. All new works based on yours will carry the same licence, so any derivatives will also allow commercial use. This is the licence used by Wikipedia, and is recommended for materials that would benefit from incorporating content from Wikipedia and similarly licenced projects.</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by-sa/4.0/deed.en</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M61" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>Topographic map</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>A map showing the shape and features of the land surface, typically including elevation, contour lines, and natural and man-made features.</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M62" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>Cadastral map</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>A map showing property boundaries, land parcels, and ownership divisions.</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M63" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>Administrative map</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>A map showing administrative or political boundaries, such as regions, districts, or provinces.</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M64" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>Aerial photograph</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>A photographic image of the ground taken from an aircraft or other airborne platform.</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M65" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>Satellite image</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>An image of the Earth's surface captured by a satellite-based sensor.</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M66" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>Geological map</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>A map showing the distribution of rock types, geological structures, and formations.</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M67" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>Thematic map</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>A map designed to display a particular subject or theme, such as the distribution of archaeological sites.</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M68" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>Site plan</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>A hand-drawn or simplified map showing the layout of a site or area, not necessarily to scale.</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M69" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>Historical map</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>A map produced in the past that documents historical geography, boundaries, or features no longer current.</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M70" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>Vegetation map</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>A map showing the distribution and type of plant cover across an area, such as forest, grassland, or cultivated land.</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H71" s="0" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M71" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>Soil map</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>A map showing the distribution, type, and characteristics of soils across an area.</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M72" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>Population map</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>A map showing the distribution or density of human population across an area.</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M73" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>A map designed for navigation, such as a nautical or aeronautical chart, showing features relevant to travel by sea or air.</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H74" s="0" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M74" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>Tourist map</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>A map designed for visitors, highlighting points of interest, facilities, and routes rather than technical survey detail.</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M75" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>Modern map</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>A current map that reflects present-day geography, boundaries, or features, as distinct from a historical map.</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>Map types</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H76" s="0" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M76" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>DZA</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H77" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M77" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H78" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M78" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H79" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M79" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H80" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M80" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>BFA</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H81" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M81" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>BDI</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M82" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H83" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M83" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H84" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M84" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H85" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M85" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>TCD</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M86" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M87" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>COG</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H88" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M88" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M89" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H90" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M90" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>DJI</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H91" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M91" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H92" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M92" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>GNQ</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H93" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M93" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>ERI</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H94" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M94" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H95" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M95" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H96" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M96" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>GAB</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M97" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F98" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H98" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M98" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F99" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H99" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M99" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>GIN</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H100" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M100" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>GNB</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H101" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M101" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H102" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M102" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>LSO</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H103" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M103" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t>LBR</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H104" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M104" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t>LBY</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F105" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H105" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M105" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H106" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M106" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t>MWI</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F107" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G107" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H107" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M107" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H108" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M108" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H109" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M109" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G110" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H110" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M110" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G111" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H111" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M111" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H112" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H113" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G114" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H114" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H115" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M115" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M116" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G117" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H117" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M117" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G118" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H118" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M118" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>SYC</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F119" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G119" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H119" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M119" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F120" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H120" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M120" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>SOM</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G121" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H121" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M121" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H122" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M122" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F123" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H123" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M123" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>SDN</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F124" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H124" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M124" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F125" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G125" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H125" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M125" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>TGO</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F126" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G126" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H126" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F127" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H127" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M127" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F128" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H128" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M128" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F129" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H129" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M129" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t>ISO 3166-1 alpha-3 (2009 revision)</t>
+        </is>
+      </c>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="F130" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G130" s="0" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H130" s="0" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="I130" s="0" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M130" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Resource type</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>20260917</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Yes (already existed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Blog post</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Resource type</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Y6SP1</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>20260917</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Yes (already existed)</t>
         </is>
       </c>
     </row>
